--- a/public/documents/pieces-reponse-2/R2-correspondance-libelles.xlsx
+++ b/public/documents/pieces-reponse-2/R2-correspondance-libelles.xlsx
@@ -121,7 +121,7 @@
     <t xml:space="preserve">Vendu 450 cl au pichet sous un bouton mal paramétré, couvert par le sur-stock de Nuits blanc.</t>
   </si>
   <si>
-    <t xml:space="preserve">R2 - Codes de vente jamais paramétrés (dont 7 bières « 100 % disparues »)</t>
+    <t xml:space="preserve">R2 - Codes de vente jamais paramétrés (dont 8 bières « 100 % disparues »)</t>
   </si>
   <si>
     <t xml:space="preserve">Le service dit ces produits « 100 % achetés non vendus ». En réalité : absents des 3 inventaires physiques ET vendu caisse = 0 dans les propres données de la société. Ce sont des codes créés mais jamais rattachés à un bouton de vente, pas des bouteilles évaporées.</t>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">- Confusion de code : un bouton générique frappé sur une référence voisine (Mouton Cadet = Bordeaux Supérieur 661236 ; Hautes Côtes de Nuits blanc 601416 confondu avec la Beaune rouge Domaine Germain).</t>
   </si>
   <si>
-    <t xml:space="preserve">- Codes fantômes : codes achetés mais jamais rattachés à un bouton de vente (7 bières, 1 eau, 1 cidre) : absents des inventaires, vendu caisse = 0.</t>
+    <t xml:space="preserve">- Codes fantômes : codes achetés mais jamais rattachés à un bouton de vente (8 bières, 1 eau, 1 cidre) : absents des inventaires, vendu caisse = 0.</t>
   </si>
   <si>
     <t xml:space="preserve">- Boutons mutualisés/génériques : un même bouton encaisse plusieurs millésimes ou plusieurs SKU (Cubis = vin maison au pichet), laissant un libellé « sur-vendu » et son frère « à 0 vendu ».</t>
@@ -367,12 +367,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -388,19 +392,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -667,125 +671,125 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -811,195 +815,195 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <f aca="false">COUNTIF(D5:D14,"Bière - code jamais paramétré")</f>
         <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1024,84 +1028,84 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>293.2</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>161.9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>394.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>218.4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>169.2</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>49.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <f aca="false">B5+B6+B7-C5-C6-C7</f>
         <v>426.8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1126,55 +1130,55 @@
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
         <v>72</v>
       </c>
     </row>
